--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.67898046919045</v>
+        <v>5.960334326243448</v>
       </c>
       <c r="D2" t="n">
-        <v>21.47482638272469</v>
+        <v>3.489659287192762</v>
       </c>
       <c r="E2" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F2" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.11040069047897</v>
+        <v>5.542940112202833</v>
       </c>
       <c r="D3" t="n">
-        <v>10.90306934486</v>
+        <v>1.771748768539749</v>
       </c>
       <c r="E3" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F3" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.23002992497837</v>
+        <v>2.962379862808985</v>
       </c>
       <c r="D4" t="n">
-        <v>16.40233725429641</v>
+        <v>2.665379803823166</v>
       </c>
       <c r="E4" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F4" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.51691158925676</v>
+        <v>3.008998133254224</v>
       </c>
       <c r="D5" t="n">
-        <v>11.93209055616179</v>
+        <v>1.938964715376291</v>
       </c>
       <c r="E5" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F5" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.10465530399047</v>
+        <v>3.754506486898452</v>
       </c>
       <c r="D6" t="n">
-        <v>24.67982993194558</v>
+        <v>4.010472363941157</v>
       </c>
       <c r="E6" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F6" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37944919526556</v>
+        <v>3.961660494230654</v>
       </c>
       <c r="D7" t="n">
-        <v>36.03175282691078</v>
+        <v>5.855159834373002</v>
       </c>
       <c r="E7" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F7" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.48513185620141</v>
+        <v>2.191333926632729</v>
       </c>
       <c r="D8" t="n">
-        <v>10.51189802081432</v>
+        <v>1.708183428382327</v>
       </c>
       <c r="E8" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F8" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.20989889314031</v>
+        <v>2.796608570135301</v>
       </c>
       <c r="D9" t="n">
-        <v>19.13765920900464</v>
+        <v>3.109869621463254</v>
       </c>
       <c r="E9" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F9" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.44226526300679</v>
+        <v>3.484368105238603</v>
       </c>
       <c r="D10" t="n">
-        <v>38.51463999291216</v>
+        <v>6.258628998848226</v>
       </c>
       <c r="E10" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F10" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.99579461292856</v>
+        <v>3.899316624600892</v>
       </c>
       <c r="D11" t="n">
-        <v>22.14289857598164</v>
+        <v>3.598221018597017</v>
       </c>
       <c r="E11" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F11" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>14.31004455808037</v>
+        <v>2.32538224068806</v>
       </c>
       <c r="D12" t="n">
-        <v>10.25327716729357</v>
+        <v>1.666157539685205</v>
       </c>
       <c r="E12" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F12" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>54.46721860620014</v>
+        <v>8.850923023507523</v>
       </c>
       <c r="D13" t="n">
-        <v>52.32576256296111</v>
+        <v>8.50293641648118</v>
       </c>
       <c r="E13" t="n">
-        <v>11.18322337075439</v>
+        <v>1.817273797747588</v>
       </c>
       <c r="F13" t="n">
-        <v>12.65532960868213</v>
+        <v>2.056491061410847</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
